--- a/src/assets/static files/increase_decrease_creditline.xlsx
+++ b/src/assets/static files/increase_decrease_creditline.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>User Name</t>
   </si>
@@ -39,6 +39,12 @@
   </si>
   <si>
     <t>Activation Date</t>
+  </si>
+  <si>
+    <t>Shubham Bhartiya</t>
+  </si>
+  <si>
+    <t>FPL-00000000001</t>
   </si>
 </sst>
 </file>
@@ -384,11 +390,21 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1">
+        <v>8080758758</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1">
+        <v>50000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>44562</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
